--- a/docs/xlsx/jobs-2026-09-19.xlsx
+++ b/docs/xlsx/jobs-2026-09-19.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="34">
   <si>
     <t>Title</t>
   </si>
@@ -38,13 +38,91 @@
   </si>
   <si>
     <t>Link</t>
+  </si>
+  <si>
+    <t>Cinema General Manager</t>
+  </si>
+  <si>
+    <t>WEST NEWTON CINEMA FOUNDATION INC</t>
+  </si>
+  <si>
+    <t>Newton, Massachusetts</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c82475e393334ac7a27f2d9a85f0713c-cinema-general-manager-west-newton-cinema-foundation-inc-newton</t>
+  </si>
+  <si>
+    <t>Development Associate</t>
+  </si>
+  <si>
+    <t>The Garden Conservancy</t>
+  </si>
+  <si>
+    <t>Greenwich, Connecticut</t>
+  </si>
+  <si>
+    <t>USD 48500.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Arts Music, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/00fd516ff2f64b7290387e6c85b2dfce-development-associate-the-garden-conservancy-greenwich</t>
+  </si>
+  <si>
+    <t>Director of Institutional Advancement</t>
+  </si>
+  <si>
+    <t>USD 102500.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Arts Music, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/43c159e3a2b24569bf566310718a2f42-director-of-institutional-advancement-the-garden-conservancy-greenwich</t>
+  </si>
+  <si>
+    <t>Director of Preservation Services</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/10c2063d4f244f0c9f3dfbca8af3ab2b-director-of-preservation-services-the-garden-conservancy-greenwich</t>
+  </si>
+  <si>
+    <t>Manager, Membership and Digital Giving</t>
+  </si>
+  <si>
+    <t>92NY</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Education, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/71205f94fd8348db90df9bd7ddea6e9b-manager-membership-and-digital-giving-92ny-new-york</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -54,6 +132,10 @@
     </font>
     <font>
       <b/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF1155CC"/>
     </font>
   </fonts>
   <fills count="2">
@@ -76,9 +158,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -514,7 +597,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -553,8 +636,130 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/xlsx/jobs-2026-09-19.xlsx
+++ b/docs/xlsx/jobs-2026-09-19.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="47">
   <si>
     <t>Title</t>
   </si>
@@ -116,6 +116,45 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/71205f94fd8348db90df9bd7ddea6e9b-manager-membership-and-digital-giving-92ny-new-york</t>
+  </si>
+  <si>
+    <t>Program &amp; Operations Manager (Builder Role)(remote or hybrid)</t>
+  </si>
+  <si>
+    <t>finEQUITY.org</t>
+  </si>
+  <si>
+    <t>Remote (Pennsylvania)</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a3629a31601049c4b30bd2c6e7a5cd42-program-operations-manager-builder-roleremote-or-hybrid-finequityorg-brooklyn</t>
+  </si>
+  <si>
+    <t>Senior Case Manager &amp; Resource Navigator</t>
+  </si>
+  <si>
+    <t>The Community Impact Fund</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 45.00 - 55.00/hour</t>
+  </si>
+  <si>
+    <t>Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3453f7e5128146dba7ee73fb81b85fb7-senior-case-manager-resource-navigator-the-community-impact-fund-sterling</t>
   </si>
 </sst>
 </file>
@@ -597,7 +636,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -751,6 +790,52 @@
         <v>33</v>
       </c>
     </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" t="s">
+        <v>45</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <hyperlinks>
@@ -759,6 +844,8 @@
     <hyperlink ref="H4" r:id="rId3"/>
     <hyperlink ref="H5" r:id="rId4"/>
     <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
